--- a/virtual-physics-lab/app/dl/SAJC_Q2f_force_extension_dataset.xlsx
+++ b/virtual-physics-lab/app/dl/SAJC_Q2f_force_extension_dataset.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,9 +101,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1069,7 +1072,7 @@
         <f>IF(A7&lt;&gt;"",0.5*(B6+B7)*(A7-A6),"")</f>
         <v/>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>work done = Σ strips</t>
         </is>
@@ -1078,7 +1081,7 @@
         <f>SUM(D6:D36)</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
@@ -1099,7 +1102,7 @@
         <f>IF(A8&lt;&gt;"",0.5*(B7+B8)*(A8-A7),"")</f>
         <v/>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>B = gradient</t>
         </is>
@@ -1108,7 +1111,7 @@
         <f>SLOPE(C6:C36,A6:A36)</f>
         <v/>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>m⁻¹</t>
         </is>
